--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.53299311513349</v>
+        <v>2.524111381209193</v>
       </c>
       <c r="D2" t="n">
-        <v>26.84008669994954</v>
+        <v>4.3615140887418</v>
       </c>
       <c r="E2" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F2" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.59051795555331</v>
+        <v>2.370959167777412</v>
       </c>
       <c r="D3" t="n">
-        <v>13.17248909322886</v>
+        <v>2.140529477649689</v>
       </c>
       <c r="E3" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F3" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.67104435090205</v>
+        <v>3.034044707021583</v>
       </c>
       <c r="D4" t="n">
-        <v>17.14951380706295</v>
+        <v>2.78679599364773</v>
       </c>
       <c r="E4" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F4" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.50854001277055</v>
+        <v>1.870137752075214</v>
       </c>
       <c r="D5" t="n">
-        <v>11.43758730538753</v>
+        <v>1.858607937125474</v>
       </c>
       <c r="E5" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F5" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>19.38747234008087</v>
+        <v>3.150464255263142</v>
       </c>
       <c r="D6" t="n">
-        <v>18.51929009639521</v>
+        <v>3.009384640664221</v>
       </c>
       <c r="E6" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F6" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>7.673902695744749</v>
+        <v>1.247009188058522</v>
       </c>
       <c r="D7" t="n">
-        <v>10.96624307632561</v>
+        <v>1.782014499902911</v>
       </c>
       <c r="E7" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F7" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.35404462401292</v>
+        <v>3.307532251402099</v>
       </c>
       <c r="D8" t="n">
-        <v>10.83391093163748</v>
+        <v>1.76051052639109</v>
       </c>
       <c r="E8" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F8" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.93254799332411</v>
+        <v>5.189039048915169</v>
       </c>
       <c r="D9" t="n">
-        <v>29.618860638052</v>
+        <v>4.813064853683451</v>
       </c>
       <c r="E9" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F9" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.37433367976407</v>
+        <v>4.448329222961662</v>
       </c>
       <c r="D10" t="n">
-        <v>26.23733702756125</v>
+        <v>4.263567266978704</v>
       </c>
       <c r="E10" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F10" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.76261373165034</v>
+        <v>3.048924731393181</v>
       </c>
       <c r="D11" t="n">
-        <v>17.66437503656203</v>
+        <v>2.87046094344133</v>
       </c>
       <c r="E11" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F11" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.25144733009628</v>
+        <v>3.940860191140646</v>
       </c>
       <c r="D12" t="n">
-        <v>27.60114460096966</v>
+        <v>4.48518599765757</v>
       </c>
       <c r="E12" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F12" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>5.024937810560445</v>
+        <v>0.8165523942160723</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5746979883188915</v>
+        <v>0.09338842310181987</v>
       </c>
       <c r="E13" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F13" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>9.297856746582481</v>
+        <v>1.510901721319653</v>
       </c>
       <c r="D14" t="n">
-        <v>4.491539445476158</v>
+        <v>0.7298751598898756</v>
       </c>
       <c r="E14" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F14" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>3.605551275463989</v>
+        <v>0.5859020822628983</v>
       </c>
       <c r="D15" t="n">
-        <v>8.586633669708856</v>
+        <v>1.395327971327689</v>
       </c>
       <c r="E15" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F15" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.60308186651023</v>
+        <v>2.373000803307913</v>
       </c>
       <c r="D16" t="n">
-        <v>10.17416390231212</v>
+        <v>1.65330163412572</v>
       </c>
       <c r="E16" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F16" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>21.38864670302741</v>
+        <v>3.475655089241954</v>
       </c>
       <c r="D17" t="n">
-        <v>16.87851669035367</v>
+        <v>2.742758962182471</v>
       </c>
       <c r="E17" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F17" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>18.78180469641617</v>
+        <v>3.052043263167628</v>
       </c>
       <c r="D18" t="n">
-        <v>20.99224502650348</v>
+        <v>3.411239816806815</v>
       </c>
       <c r="E18" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F18" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>18.33024832217235</v>
+        <v>2.978665352353007</v>
       </c>
       <c r="D19" t="n">
-        <v>24.62071564760928</v>
+        <v>4.000866292736508</v>
       </c>
       <c r="E19" t="n">
-        <v>7.233666860864586</v>
+        <v>1.175470864890495</v>
       </c>
       <c r="F19" t="n">
-        <v>8.127656121398537</v>
+        <v>1.320744119727262</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
